--- a/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לא המשוגע היחידי (2026)</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:17-01-18</v>
+        <v>2026  11:10-01-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24440&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לא המשוגע היחידי (2026)</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  11:47-01-17</v>
+        <v>2026  11:48-01-17</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 (2026)</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -536,18 +536,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 (2026)</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026  22:40-01-01</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B7" t="str">
         <v>2025  02:16-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -711,18 +711,18 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -746,18 +746,18 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B11" t="str">
         <v>2025  02:09-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -781,18 +781,18 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -816,18 +816,18 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B13" t="str">
         <v>2025  02:05-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -851,18 +851,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -886,18 +886,18 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -921,7 +921,7 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23:52</v>
+        <v>22:43</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>02:10</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -474,22 +474,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-12-31</v>
+        <v>2026-01-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>02:12</v>
+        <v>23:52</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,468 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>11:48</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>08:41</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>08:40</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>02:18</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>02:16</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>02:14</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B11" t="str">
         <v>2025-12-31</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C11" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D4" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
+      <c r="D11" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>02:10</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>02:08</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>02:05</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>02:04</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>02:02</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>